--- a/data/netz_excels/knoten_excel.xlsx
+++ b/data/netz_excels/knoten_excel.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,16 +520,16 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>POINT (568211.8929999999 6003333.9212)</t>
+          <t>POINT (568197.75 6003386.727)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6B4100-011</t>
+          <t>6B0402-125</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -549,16 +549,16 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>POINT (568197.75 6003386.727)</t>
+          <t>POINT (568213.4645 6003318.0075)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6B0402-125</t>
+          <t>6B4100-003</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,26 +568,30 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MUFFE</t>
+          <t>KVS</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6-REIHIG</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>POINT (568213.4645 6003318.0075)</t>
+          <t>POINT (568117.207 6003363.45425)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6B4100-003</t>
+          <t>6B0402-209</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -597,30 +601,26 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KVS</t>
+          <t>MUFFE</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>6-REIHIG</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>POINT (568117.207 6003363.45425)</t>
+          <t>POINT (568231.324 6003372.195)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6B0402-209</t>
+          <t>6B0402-043</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -640,16 +640,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>POINT (568231.324 6003372.195)</t>
+          <t>POINT (568293.621 6003393.373)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6B0402-043</t>
+          <t>6B0402-037</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -669,16 +669,16 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>POINT (568293.621 6003393.373)</t>
+          <t>POINT (568052.899 6003322.592999999)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6B0402-037</t>
+          <t>6B0402-017</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -688,59 +688,59 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MUFFE</t>
+          <t>KVS</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6-REIHIG</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>POINT (568052.899 6003322.592999999)</t>
+          <t>POINT (568341.43 6003430.613999999)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6B0402-017</t>
+          <t>6B0402-272</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KVS</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>6-REIHIG</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>POINT (568341.43 6003430.613999999)</t>
+          <t>POINT (568280.9420000002 6003488.267)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6B0402-272</t>
+          <t>6B0402-282</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -760,16 +760,16 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>POINT (568280.9420000002 6003488.267)</t>
+          <t>POINT (568132.06 6003393.532999999)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6B0402-282</t>
+          <t>6B0402-318</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -789,16 +789,16 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>POINT (568132.06 6003393.532999999)</t>
+          <t>POINT (568165.255 6003357.682)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6B0402-318</t>
+          <t>6B0402-320</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -818,16 +818,16 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>POINT (568165.255 6003357.682)</t>
+          <t>POINT (568141.584 6003362.07)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>6B0402-320</t>
+          <t>6B0402-324</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -847,16 +847,16 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>POINT (568141.584 6003362.07)</t>
+          <t>POINT (568124.828 6003351.766)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6B0402-324</t>
+          <t>6B0402-328</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -876,16 +876,16 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>POINT (568124.828 6003351.766)</t>
+          <t>POINT (568118.5940000002 6003322.377)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6B0402-328</t>
+          <t>6B0402-332</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -905,16 +905,16 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>POINT (568118.5940000002 6003322.377)</t>
+          <t>POINT (568092.305 6003345.958999999)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6B0402-332</t>
+          <t>6B0402-334</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -934,16 +934,16 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>POINT (568092.305 6003345.958999999)</t>
+          <t>POINT (568077.7410000002 6003330.142)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6B0402-334</t>
+          <t>6B0402-336</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -963,16 +963,16 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>POINT (568077.7410000002 6003330.142)</t>
+          <t>POINT (568234.589 6003477.063000001)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6B0402-336</t>
+          <t>6B0402-270</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -988,53 +988,53 @@
       <c r="F19" t="n">
         <v>0</v>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NH_GR.II_TM</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>POINT (568225.205 6003478.308)</t>
+          <t>POINT (568241.323 6003388.954)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6B0402-252</t>
+          <t>6B0402-103</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>MUFFE</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>NH_GR.2/3X63A</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>POINT (568234.589 6003477.063000001)</t>
+          <t>POINT (568064.2603999999 6003334.779999999)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6B0402-270</t>
+          <t>6B0402-109</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1044,35 +1044,31 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>MUFFE</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>NH_GR.II_TM</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>POINT (568241.323 6003388.954)</t>
+          <t>POINT (568062.5570000001 6003328.561)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6B0402-103</t>
+          <t>6B0402-338</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1087,16 +1083,16 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POINT (568101.125 6003375.565000001)</t>
+          <t>POINT (568063.037 6003303.806999999)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6B0402-378</t>
+          <t>6B0401-576</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1106,26 +1102,30 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MUFFE</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NH_GR.00_3X40A</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POINT (568064.2603999999 6003334.779999999)</t>
+          <t>POINT (568205.069 6003396.322)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6B0402-109</t>
+          <t>6B0402-346</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1145,21 +1145,21 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POINT (568062.5570000001 6003328.561)</t>
+          <t>POINT (568209.0829999999 6003386.439)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6B0402-338</t>
+          <t>6B0402-129</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1174,49 +1174,45 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POINT (568063.037 6003303.806999999)</t>
+          <t>POINT (568067.7580000001 6003339.723)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6B0401-576</t>
+          <t>6B0402-376</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>MUFFE</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NH_GR.00_3X40A</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>POINT (568205.069 6003396.322)</t>
+          <t>POINT (568117.026 6003357.151)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6B0402-346</t>
+          <t>6B0402-370</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1236,21 +1232,21 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>POINT (568209.0829999999 6003386.439)</t>
+          <t>POINT (568083.274 6003355.104)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6B0402-129</t>
+          <t>6B0402-310</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1265,21 +1261,21 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>POINT (568067.7580000001 6003339.723)</t>
+          <t>POINT (568302.846 6003421.297)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6B0402-376</t>
+          <t>6B0402-242</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1294,21 +1290,21 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>POINT (568117.026 6003357.151)</t>
+          <t>POINT (568340.7859999998 6003415.053999999)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6B0402-370</t>
+          <t>6B0402-292</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1323,16 +1319,16 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>POINT (568083.274 6003355.104)</t>
+          <t>POINT (568322.213 6003429.264000001)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>6B0402-310</t>
+          <t>6B0402-306</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1348,25 +1344,29 @@
       <c r="F31" t="n">
         <v>0</v>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>NH_GR.00_3X63A</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>POINT (568302.846 6003421.297)</t>
+          <t>POINT (568323.621 6003395.917)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>6B0402-242</t>
+          <t>6B0402-304</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1381,21 +1381,21 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>POINT (568340.7859999998 6003415.053999999)</t>
+          <t>POINT (568221.568 6003334.599000001)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6B0402-292</t>
+          <t>6B4100-041</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1410,54 +1410,36 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>POINT (568322.213 6003429.264000001)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>6B0402-306</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>SAB</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>MUFFE</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>NH_GR.00_3X63A</t>
-        </is>
-      </c>
+          <t>POINT (568290.321 6003415.078999999)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>POINT (568323.621 6003395.917)</t>
+          <t>POINT (568177.967 6003385.548000001)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>6B0402-304</t>
+          <t>6B0402-081</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1472,16 +1454,16 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>POINT (568221.568 6003334.599000001)</t>
+          <t>POINT (568162.067 6003373.704)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6B4100-041</t>
+          <t>6B0402-322</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1501,36 +1483,50 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>POINT (568290.321 6003415.078999999)</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>POINT (568122.33 6003364.115499999)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>6B0402-374</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SAB</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>MUFFE</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
       <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>POINT (568177.967 6003385.548000001)</t>
+          <t>POINT (568091.9370000002 6003356.443)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6B0402-081</t>
+          <t>6B0402-372</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>SAB</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1545,16 +1541,16 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>POINT (568162.067 6003373.704)</t>
+          <t>POINT (568377.267 6003401.699)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>6B0402-322</t>
+          <t>6B0402-105</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1564,31 +1560,35 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MUFFE</t>
+          <t>KVS</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>6-reihig</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>POINT (568122.33 6003364.115499999)</t>
+          <t>POINT (568109.518 6003363.038999999)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>6B0402-374</t>
+          <t>6B0402-248</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAB</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1603,16 +1603,16 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>POINT (568091.9370000002 6003356.443)</t>
+          <t>POINT (568313.681 6003395.256)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>6B0402-372</t>
+          <t>6B0402-276</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1632,152 +1632,32 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>POINT (568377.267 6003401.699)</t>
+          <t>POINT (568345.011 6003397.712)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>6B0402-105</t>
+          <t>6B0402-294</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KVS</t>
+          <t>MUFFE</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>6-reihig</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>POINT (568109.518 6003363.038999999)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>6B0402-248</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>MUFFE</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>POINT (568080.957 6003360.351999999)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>6B0402-348</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SAB</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>NH_GR.00_1X35A</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>POINT (568313.681 6003395.256)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>6B0402-276</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SAB</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>MUFFE</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>POINT (568345.011 6003397.712)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>6B0402-294</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>MUFFE</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
